--- a/jogos_2025-02-27.xlsx
+++ b/jogos_2025-02-27.xlsx
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M3" t="n">
         <v>2.8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2.65</v>
       </c>
       <c r="N3" t="n">
         <v>2.8</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '33']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45715.35416666666</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="N4" t="n">
         <v>2.8</v>
       </c>
       <c r="O4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['11', '33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45715.35416666666</v>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Albirex Niigata S</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,65 +1056,65 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.17</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>3.93</v>
+        <v>6.6</v>
       </c>
       <c r="N5" t="n">
-        <v>2.81</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6</v>
+        <v>1.44</v>
       </c>
       <c r="P5" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="Q5" t="n">
+        <v>9</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.25</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.91</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>8.300000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.56</v>
+        <v>4.91</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['39', '45', '45+1', '89']</t>
+          <t>['3', '7', '52', '71', '90']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.61</v>
+        <v>1.06</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.2</v>
+        <v>1.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45715.36458333334</v>
@@ -1159,91 +1159,91 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Albirex Niigata S</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S6" t="n">
         <v>5</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>9</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6.5</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>11.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.91</v>
+        <v>3.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.42</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['3', '7', '52', '71', '90']</t>
+          <t>['39', '45', '45+1', '89']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.06</v>
+        <v>1.61</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.22</v>
+        <v>2.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4</v>
+        <v>1.62</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45715.36458333334</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="S7" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="W7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.58</v>
       </c>
-      <c r="X7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AI7" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45715.41666666666</v>
@@ -1407,35 +1407,35 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Pahang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.1</v>
       </c>
-      <c r="M8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '20', '28', '58', '90']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45715.41666666666</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tataouine</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EGS Gafsa</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N9" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T9" t="n">
         <v>3.75</v>
       </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.68</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.15</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['3']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.1</v>
       </c>
-      <c r="AC9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['36']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45715.41666666666</v>
@@ -1665,119 +1665,119 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['53', '62', '83']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.91</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45715.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,19 +1933,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="M12" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
         <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="T12" t="n">
-        <v>4.75</v>
+        <v>3.82</v>
       </c>
       <c r="U12" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['90+12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['67', '84']</t>
+          <t>['53', '62', '83']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45715.41666666666</v>
@@ -2052,29 +2052,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.65</v>
       </c>
-      <c r="M13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.22</v>
-      </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.6</v>
+        <v>8.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.6</v>
+        <v>2.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+12']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67', '84']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.15</v>
+        <v>1.52</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45715.41666666666</v>
@@ -2181,119 +2181,119 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pahang</t>
+          <t>Tataouine</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>EGS Gafsa</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>5</v>
-      </c>
       <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="M14" t="n">
         <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['36']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>2.75</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['40']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['3', '20', '28', '58', '90']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45715.41666666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.88</v>
+        <v>3.97</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>1.73</v>
       </c>
       <c r="N16" t="n">
-        <v>2.1</v>
+        <v>3.57</v>
       </c>
       <c r="O16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.4</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
-        <v>6.25</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>2.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.09</v>
+        <v>1.48</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.8</v>
+        <v>4.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4', '71']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['25', '55', '70', '77']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.77</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.57</v>
+        <v>3.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45715.44791666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T17" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="U17" t="n">
         <v>1.73</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.1</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X17" t="n">
-        <v>2.4</v>
+        <v>6.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.47</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.48</v>
+        <v>3.09</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['25', '55', '70', '77']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['45+4', '71']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['55']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45715.44791666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2854,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.28</v>
+        <v>2.92</v>
       </c>
       <c r="M19" t="n">
-        <v>3.02</v>
+        <v>2.76</v>
       </c>
       <c r="N19" t="n">
-        <v>3.34</v>
+        <v>2.74</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q19" t="n">
-        <v>4</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T19" t="n">
-        <v>4</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.5</v>
       </c>
-      <c r="X19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['11', '53']</t>
+          <t>['27', '58']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['20', '54']</t>
+          <t>['84', '90+11']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45715.45833333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="O21" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.26</v>
+        <v>1.5</v>
       </c>
       <c r="X21" t="n">
-        <v>3.22</v>
+        <v>2.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AC21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['11', '53']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['20', '54']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['69']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45715.45833333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.18</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="X22" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.91</v>
       </c>
-      <c r="Y22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['27', '58']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['84', '90+11']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45715.45833333334</v>
